--- a/backtest_runs/20260410_193731/by_symbol/LEUL/LEUL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/LEUL/LEUL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>104396.14</v>
@@ -771,7 +771,7 @@
         <v>-1465.379999999994</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>110048.32</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>110048.32</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>110048.32</v>
@@ -1185,7 +1185,7 @@
         <v>-10152.99</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>99895.33</v>
@@ -1415,7 +1415,7 @@
         <v>-9908.76</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>100593.13</v>
@@ -1507,7 +1507,7 @@
         <v>-2442.299999999997</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>98150.83</v>
